--- a/AAII_Financials/Yearly/POM_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/POM_YR_FIN.xlsx
@@ -1624,7 +1624,7 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>12400</v>
+        <v>2800</v>
       </c>
       <c r="E43" s="3">
         <v>1300</v>
@@ -1684,7 +1684,7 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>100</v>
+        <v>9400</v>
       </c>
       <c r="E45" s="3">
         <v>1400</v>
@@ -2072,7 +2072,7 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>8500</v>
+        <v>2100</v>
       </c>
       <c r="E59" s="3">
         <v>2300</v>
